--- a/Master/2119r1/2119r1 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/2119r1/2119r1 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1534,442 +1534,462 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>3.139</v>
+        <v>3.251</v>
       </c>
       <c r="B55" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>5.6287</v>
+        <v>5.599</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-0.5124</v>
+        <v>-2.0848</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0196</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>2.24</v>
+        <v>3.139</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>5.6539</v>
+        <v>5.6287</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>-0.5804</v>
+        <v>-0.5124</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>5.7064</v>
+        <v>5.6539</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-0.6717</v>
+        <v>-0.5804</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0182</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>1.241</v>
+        <v>2.14</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>5.7262</v>
+        <v>5.7064</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.6717</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>1.141</v>
+        <v>1.241</v>
       </c>
       <c r="B59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>5.7748</v>
+        <v>5.7262</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-0.833</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0155</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
-        <v>6.242</v>
+        <v>1.141</v>
       </c>
       <c r="B60" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>5.7919</v>
+        <v>5.7748</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>-0.6506</v>
+        <v>-0.833</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>0.0003</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n">
-        <v>6.142</v>
+        <v>6.242</v>
       </c>
       <c r="B61" s="6" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>5.8369</v>
+        <v>5.7919</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>-0.7468</v>
+        <v>-0.6506</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>0.0144</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n">
-        <v>5.243</v>
+        <v>6.142</v>
       </c>
       <c r="B62" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>5.8514</v>
+        <v>5.8369</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>-0.8175</v>
+        <v>-0.7468</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>0.0002</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>5.143</v>
+        <v>5.243</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>5.8905</v>
+        <v>5.8514</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-0.9122</v>
+        <v>-0.8175</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0124</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>4.244</v>
+        <v>5.143</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>5.9034</v>
+        <v>5.8905</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>-0.9825</v>
+        <v>-0.9122</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.0002</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>4.144</v>
+        <v>4.244</v>
       </c>
       <c r="B65" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>5.9397</v>
+        <v>5.9034</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-1.0826</v>
+        <v>-0.9825</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0114</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>3.245</v>
+        <v>4.144</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>5.9501</v>
+        <v>5.9397</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>-1.1574</v>
+        <v>-1.0826</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>3.145</v>
+        <v>3.245</v>
       </c>
       <c r="B67" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>5.982</v>
+        <v>5.9501</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-1.2576</v>
+        <v>-1.1574</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0097</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>2.146</v>
+        <v>3.145</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>6.019</v>
+        <v>5.982</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>-1.4345</v>
+        <v>-1.2576</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
-        <v>1.147</v>
+        <v>2.146</v>
       </c>
       <c r="B69" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>6.0497</v>
+        <v>6.019</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>-1.6119</v>
+        <v>-1.4345</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.0068</v>
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n">
-        <v>6.148</v>
+        <v>1.147</v>
       </c>
       <c r="B70" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C70" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>6.075</v>
+        <v>6.0497</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>-1.5399</v>
+        <v>-1.6119</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.0057</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n">
-        <v>5.149</v>
+        <v>6.148</v>
       </c>
       <c r="B71" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>6.0951</v>
+        <v>6.075</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>-1.7202</v>
+        <v>-1.5399</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>0.0041</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n">
-        <v>4.15</v>
+        <v>5.149</v>
       </c>
       <c r="B72" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>6.109</v>
+        <v>6.0951</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>-1.898</v>
+        <v>-1.7202</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n">
-        <v>3.151</v>
+        <v>4.15</v>
       </c>
       <c r="B73" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>6.1166</v>
+        <v>6.109</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>-2.065</v>
+        <v>-1.898</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>0.0009</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n">
-        <v>2.152</v>
+        <v>3.151</v>
       </c>
       <c r="B74" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>6.1206</v>
+        <v>6.1166</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>-2.1931</v>
+        <v>-2.065</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>0.0013</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n">
+        <v>2.152</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>6.1206</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>-2.1931</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>0.0013</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n">
         <v>1.153</v>
       </c>
-      <c r="B75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" s="7" t="n">
+      <c r="B76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="7" t="n">
         <v>6.1224</v>
       </c>
-      <c r="E75" s="7" t="n">
+      <c r="E76" s="7" t="n">
         <v>-2.2991</v>
       </c>
-      <c r="F75" s="7" t="n">
+      <c r="F76" s="7" t="n">
         <v>0.0002</v>
       </c>
     </row>
-    <row r="77">
-      <c r="E77" s="8" t="inlineStr">
+    <row r="78">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F77" s="9" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="E78" s="8" t="inlineStr">
+      <c r="F78" s="9" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F78" s="10" t="n">
-        <v>1.5216</v>
+      <c r="F79" s="10" t="n">
+        <v>1.5221</v>
       </c>
     </row>
   </sheetData>
